--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ34"/>
+  <dimension ref="A1:BR34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -989,6 +994,9 @@
       <c r="BQ2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BR2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1200,6 +1208,9 @@
       <c r="BQ3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BR3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1411,6 +1422,9 @@
       <c r="BQ4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BR4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1622,6 +1636,9 @@
       <c r="BQ5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BR5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1833,6 +1850,9 @@
       <c r="BQ6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BR6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2044,6 +2064,9 @@
       <c r="BQ7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BR7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2255,6 +2278,9 @@
       <c r="BQ8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BR8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2466,6 +2492,9 @@
       <c r="BQ9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BR9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2677,6 +2706,9 @@
       <c r="BQ10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BR10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2888,6 +2920,9 @@
       <c r="BQ11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BR11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3099,6 +3134,9 @@
       <c r="BQ12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BR12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3310,6 +3348,9 @@
       <c r="BQ13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BR13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3521,6 +3562,9 @@
       <c r="BQ14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BR14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3732,6 +3776,9 @@
       <c r="BQ15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BR15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3943,6 +3990,9 @@
       <c r="BQ16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BR16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4154,6 +4204,9 @@
       <c r="BQ17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BR17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4365,6 +4418,9 @@
       <c r="BQ18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BR18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4576,6 +4632,9 @@
       <c r="BQ19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BR19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4787,6 +4846,9 @@
       <c r="BQ20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BR20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4998,6 +5060,9 @@
       <c r="BQ21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BR21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5209,6 +5274,9 @@
       <c r="BQ22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BR22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5420,6 +5488,9 @@
       <c r="BQ23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BR23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5631,6 +5702,9 @@
       <c r="BQ24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BR24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5842,6 +5916,9 @@
       <c r="BQ25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BR25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6053,6 +6130,9 @@
       <c r="BQ26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BR26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6264,6 +6344,9 @@
       <c r="BQ27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BR27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6475,6 +6558,9 @@
       <c r="BQ28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BR28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6686,6 +6772,9 @@
       <c r="BQ29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BR29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6897,6 +6986,9 @@
       <c r="BQ30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BR30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7108,6 +7200,9 @@
       <c r="BQ31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BR31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7319,6 +7414,9 @@
       <c r="BQ32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BR32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7530,6 +7628,9 @@
       <c r="BQ33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BR33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7739,6 +7840,9 @@
         <v>51.36</v>
       </c>
       <c r="BQ34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BR34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR34"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -997,6 +1002,9 @@
       <c r="BR2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BS2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1211,6 +1219,9 @@
       <c r="BR3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BS3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1425,6 +1436,9 @@
       <c r="BR4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BS4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1639,6 +1653,9 @@
       <c r="BR5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BS5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1853,6 +1870,9 @@
       <c r="BR6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BS6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2067,6 +2087,9 @@
       <c r="BR7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BS7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2281,6 +2304,9 @@
       <c r="BR8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BS8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2495,6 +2521,9 @@
       <c r="BR9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BS9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2709,6 +2738,9 @@
       <c r="BR10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BS10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2923,6 +2955,9 @@
       <c r="BR11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BS11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3137,6 +3172,9 @@
       <c r="BR12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BS12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3351,6 +3389,9 @@
       <c r="BR13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BS13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3565,6 +3606,9 @@
       <c r="BR14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BS14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3779,6 +3823,9 @@
       <c r="BR15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BS15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3993,6 +4040,9 @@
       <c r="BR16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BS16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4207,6 +4257,9 @@
       <c r="BR17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BS17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4421,6 +4474,9 @@
       <c r="BR18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BS18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4635,6 +4691,9 @@
       <c r="BR19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BS19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4849,6 +4908,9 @@
       <c r="BR20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BS20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5063,6 +5125,9 @@
       <c r="BR21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BS21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5277,6 +5342,9 @@
       <c r="BR22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BS22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5491,6 +5559,9 @@
       <c r="BR23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BS23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5705,6 +5776,9 @@
       <c r="BR24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BS24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5919,6 +5993,9 @@
       <c r="BR25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BS25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6133,6 +6210,9 @@
       <c r="BR26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BS26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6347,6 +6427,9 @@
       <c r="BR27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BS27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6561,6 +6644,9 @@
       <c r="BR28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BS28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6775,6 +6861,9 @@
       <c r="BR29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BS29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6989,6 +7078,9 @@
       <c r="BR30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BS30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7203,6 +7295,9 @@
       <c r="BR31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BS31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7417,6 +7512,9 @@
       <c r="BR32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BS32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7631,6 +7729,9 @@
       <c r="BR33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BS33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7843,6 +7944,9 @@
         <v>51.36</v>
       </c>
       <c r="BR34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BS34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS34"/>
+  <dimension ref="A1:BT34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1005,6 +1010,9 @@
       <c r="BS2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BT2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1222,6 +1230,9 @@
       <c r="BS3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BT3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1439,6 +1450,9 @@
       <c r="BS4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BT4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1656,6 +1670,9 @@
       <c r="BS5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BT5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1873,6 +1890,9 @@
       <c r="BS6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BT6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2090,6 +2110,9 @@
       <c r="BS7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BT7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2307,6 +2330,9 @@
       <c r="BS8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BT8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2524,6 +2550,9 @@
       <c r="BS9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BT9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2741,6 +2770,9 @@
       <c r="BS10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BT10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2958,6 +2990,9 @@
       <c r="BS11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BT11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3175,6 +3210,9 @@
       <c r="BS12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BT12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3392,6 +3430,9 @@
       <c r="BS13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BT13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3609,6 +3650,9 @@
       <c r="BS14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BT14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3826,6 +3870,9 @@
       <c r="BS15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BT15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4043,6 +4090,9 @@
       <c r="BS16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BT16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4260,6 +4310,9 @@
       <c r="BS17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BT17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4477,6 +4530,9 @@
       <c r="BS18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BT18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4694,6 +4750,9 @@
       <c r="BS19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BT19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4911,6 +4970,9 @@
       <c r="BS20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BT20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5128,6 +5190,9 @@
       <c r="BS21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BT21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5345,6 +5410,9 @@
       <c r="BS22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BT22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5562,6 +5630,9 @@
       <c r="BS23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BT23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5779,6 +5850,9 @@
       <c r="BS24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BT24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5996,6 +6070,9 @@
       <c r="BS25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BT25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6213,6 +6290,9 @@
       <c r="BS26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BT26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6430,6 +6510,9 @@
       <c r="BS27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BT27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6647,6 +6730,9 @@
       <c r="BS28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BT28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6864,6 +6950,9 @@
       <c r="BS29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BT29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7081,6 +7170,9 @@
       <c r="BS30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BT30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7298,6 +7390,9 @@
       <c r="BS31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BT31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7515,6 +7610,9 @@
       <c r="BS32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BT32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7732,6 +7830,9 @@
       <c r="BS33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BT33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7947,6 +8048,9 @@
         <v>51.36</v>
       </c>
       <c r="BS34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BT34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT34"/>
+  <dimension ref="A1:BU34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1013,6 +1018,9 @@
       <c r="BT2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BU2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1233,6 +1241,9 @@
       <c r="BT3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BU3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1453,6 +1464,9 @@
       <c r="BT4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BU4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1673,6 +1687,9 @@
       <c r="BT5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BU5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1893,6 +1910,9 @@
       <c r="BT6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BU6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2113,6 +2133,9 @@
       <c r="BT7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BU7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2333,6 +2356,9 @@
       <c r="BT8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BU8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2553,6 +2579,9 @@
       <c r="BT9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BU9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2773,6 +2802,9 @@
       <c r="BT10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BU10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2993,6 +3025,9 @@
       <c r="BT11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BU11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3213,6 +3248,9 @@
       <c r="BT12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BU12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3433,6 +3471,9 @@
       <c r="BT13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BU13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3653,6 +3694,9 @@
       <c r="BT14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BU14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3873,6 +3917,9 @@
       <c r="BT15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BU15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4093,6 +4140,9 @@
       <c r="BT16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BU16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4313,6 +4363,9 @@
       <c r="BT17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BU17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4533,6 +4586,9 @@
       <c r="BT18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BU18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4753,6 +4809,9 @@
       <c r="BT19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BU19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4973,6 +5032,9 @@
       <c r="BT20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BU20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5193,6 +5255,9 @@
       <c r="BT21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BU21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5413,6 +5478,9 @@
       <c r="BT22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BU22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5633,6 +5701,9 @@
       <c r="BT23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BU23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5853,6 +5924,9 @@
       <c r="BT24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BU24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6073,6 +6147,9 @@
       <c r="BT25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BU25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6293,6 +6370,9 @@
       <c r="BT26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BU26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6513,6 +6593,9 @@
       <c r="BT27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BU27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6733,6 +6816,9 @@
       <c r="BT28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BU28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6953,6 +7039,9 @@
       <c r="BT29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BU29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7173,6 +7262,9 @@
       <c r="BT30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BU30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7393,6 +7485,9 @@
       <c r="BT31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BU31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7613,6 +7708,9 @@
       <c r="BT32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BU32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7833,6 +7931,9 @@
       <c r="BT33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BU33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8051,6 +8152,9 @@
         <v>51.36</v>
       </c>
       <c r="BT34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BU34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU34"/>
+  <dimension ref="A1:BV34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1021,6 +1026,9 @@
       <c r="BU2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BV2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1244,6 +1252,9 @@
       <c r="BU3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BV3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1467,6 +1478,9 @@
       <c r="BU4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BV4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1690,6 +1704,9 @@
       <c r="BU5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BV5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1913,6 +1930,9 @@
       <c r="BU6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BV6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2136,6 +2156,9 @@
       <c r="BU7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BV7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2359,6 +2382,9 @@
       <c r="BU8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BV8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2582,6 +2608,9 @@
       <c r="BU9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BV9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2805,6 +2834,9 @@
       <c r="BU10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BV10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3028,6 +3060,9 @@
       <c r="BU11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BV11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3251,6 +3286,9 @@
       <c r="BU12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BV12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3474,6 +3512,9 @@
       <c r="BU13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BV13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3697,6 +3738,9 @@
       <c r="BU14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BV14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3920,6 +3964,9 @@
       <c r="BU15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BV15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4143,6 +4190,9 @@
       <c r="BU16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BV16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4366,6 +4416,9 @@
       <c r="BU17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BV17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4589,6 +4642,9 @@
       <c r="BU18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BV18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4812,6 +4868,9 @@
       <c r="BU19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BV19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5035,6 +5094,9 @@
       <c r="BU20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BV20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5258,6 +5320,9 @@
       <c r="BU21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BV21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5481,6 +5546,9 @@
       <c r="BU22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BV22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5704,6 +5772,9 @@
       <c r="BU23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BV23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5927,6 +5998,9 @@
       <c r="BU24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BV24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6150,6 +6224,9 @@
       <c r="BU25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BV25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6373,6 +6450,9 @@
       <c r="BU26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BV26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6596,6 +6676,9 @@
       <c r="BU27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BV27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6819,6 +6902,9 @@
       <c r="BU28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BV28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7042,6 +7128,9 @@
       <c r="BU29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BV29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7265,6 +7354,9 @@
       <c r="BU30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BV30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7488,6 +7580,9 @@
       <c r="BU31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BV31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7711,6 +7806,9 @@
       <c r="BU32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BV32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7934,6 +8032,9 @@
       <c r="BU33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BV33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8155,6 +8256,9 @@
         <v>51.36</v>
       </c>
       <c r="BU34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BV34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV34"/>
+  <dimension ref="A1:BW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1029,6 +1034,9 @@
       <c r="BV2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BW2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1255,6 +1263,9 @@
       <c r="BV3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BW3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1481,6 +1492,9 @@
       <c r="BV4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BW4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1707,6 +1721,9 @@
       <c r="BV5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BW5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1933,6 +1950,9 @@
       <c r="BV6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BW6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2159,6 +2179,9 @@
       <c r="BV7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BW7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2385,6 +2408,9 @@
       <c r="BV8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BW8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2611,6 +2637,9 @@
       <c r="BV9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BW9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2837,6 +2866,9 @@
       <c r="BV10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BW10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3063,6 +3095,9 @@
       <c r="BV11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BW11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3289,6 +3324,9 @@
       <c r="BV12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BW12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3515,6 +3553,9 @@
       <c r="BV13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BW13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3741,6 +3782,9 @@
       <c r="BV14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BW14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3967,6 +4011,9 @@
       <c r="BV15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BW15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4193,6 +4240,9 @@
       <c r="BV16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BW16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4419,6 +4469,9 @@
       <c r="BV17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BW17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4645,6 +4698,9 @@
       <c r="BV18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BW18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4871,6 +4927,9 @@
       <c r="BV19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BW19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5097,6 +5156,9 @@
       <c r="BV20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BW20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5323,6 +5385,9 @@
       <c r="BV21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BW21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5549,6 +5614,9 @@
       <c r="BV22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BW22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5775,6 +5843,9 @@
       <c r="BV23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BW23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6001,6 +6072,9 @@
       <c r="BV24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BW24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6227,6 +6301,9 @@
       <c r="BV25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BW25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6453,6 +6530,9 @@
       <c r="BV26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BW26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6679,6 +6759,9 @@
       <c r="BV27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BW27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6905,6 +6988,9 @@
       <c r="BV28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BW28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7131,6 +7217,9 @@
       <c r="BV29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BW29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7357,6 +7446,9 @@
       <c r="BV30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BW30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7583,6 +7675,9 @@
       <c r="BV31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BW31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7809,6 +7904,9 @@
       <c r="BV32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BW32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8035,6 +8133,9 @@
       <c r="BV33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BW33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8259,6 +8360,9 @@
         <v>51.36</v>
       </c>
       <c r="BV34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BW34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW34"/>
+  <dimension ref="A1:BX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1037,6 +1042,9 @@
       <c r="BW2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BX2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1266,6 +1274,9 @@
       <c r="BW3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BX3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1495,6 +1506,9 @@
       <c r="BW4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BX4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1724,6 +1738,9 @@
       <c r="BW5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BX5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1953,6 +1970,9 @@
       <c r="BW6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BX6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2182,6 +2202,9 @@
       <c r="BW7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BX7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2411,6 +2434,9 @@
       <c r="BW8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BX8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2640,6 +2666,9 @@
       <c r="BW9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BX9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2869,6 +2898,9 @@
       <c r="BW10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BX10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3098,6 +3130,9 @@
       <c r="BW11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BX11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3327,6 +3362,9 @@
       <c r="BW12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BX12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3556,6 +3594,9 @@
       <c r="BW13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BX13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3785,6 +3826,9 @@
       <c r="BW14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BX14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4014,6 +4058,9 @@
       <c r="BW15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BX15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4243,6 +4290,9 @@
       <c r="BW16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BX16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4472,6 +4522,9 @@
       <c r="BW17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BX17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4701,6 +4754,9 @@
       <c r="BW18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BX18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4930,6 +4986,9 @@
       <c r="BW19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BX19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5159,6 +5218,9 @@
       <c r="BW20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BX20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5388,6 +5450,9 @@
       <c r="BW21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BX21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5617,6 +5682,9 @@
       <c r="BW22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BX22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5846,6 +5914,9 @@
       <c r="BW23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BX23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6075,6 +6146,9 @@
       <c r="BW24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BX24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6304,6 +6378,9 @@
       <c r="BW25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BX25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6533,6 +6610,9 @@
       <c r="BW26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BX26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6762,6 +6842,9 @@
       <c r="BW27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BX27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6991,6 +7074,9 @@
       <c r="BW28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BX28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7220,6 +7306,9 @@
       <c r="BW29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BX29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7449,6 +7538,9 @@
       <c r="BW30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BX30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7678,6 +7770,9 @@
       <c r="BW31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BX31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7907,6 +8002,9 @@
       <c r="BW32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BX32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8136,6 +8234,9 @@
       <c r="BW33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BX33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8363,6 +8464,9 @@
         <v>51.36</v>
       </c>
       <c r="BW34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BX34" t="n">
         <v>51.36</v>
       </c>
     </row>
